--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63807.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63807.xlsx
@@ -530,7 +530,11 @@
           <t>Prénom</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -538,7 +542,11 @@
           <t>Nom</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
